--- a/src/thingsboard_automation/documentation/test_cases.xlsx
+++ b/src/thingsboard_automation/documentation/test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhilashbabu/Documents/ABB/thingsboard-automation/src/thingsboard_automation/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9C94089-5453-8145-A263-48150F303029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D063E9A-ADFE-8147-A38A-1E2BC654C9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{D8055547-9248-5547-823D-40C3B2E66A2C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="176">
   <si>
     <t>TC ID</t>
   </si>
@@ -486,6 +486,153 @@
   </si>
   <si>
     <t>Evidence / UI</t>
+  </si>
+  <si>
+    <t>TC-026</t>
+  </si>
+  <si>
+    <t>Login with empty username</t>
+  </si>
+  <si>
+    <t>Leave username empty and click Sign in</t>
+  </si>
+  <si>
+    <t>Validation message is displayed and login is prevented</t>
+  </si>
+  <si>
+    <t>Negative / UI</t>
+  </si>
+  <si>
+    <t>TC-027</t>
+  </si>
+  <si>
+    <t>Login with empty password</t>
+  </si>
+  <si>
+    <t>Enter username, leave password empty and click Sign in</t>
+  </si>
+  <si>
+    <t>TC-028</t>
+  </si>
+  <si>
+    <t>Login with both fields empty</t>
+  </si>
+  <si>
+    <t>Leave username and password empty and click Sign in</t>
+  </si>
+  <si>
+    <t>Required field validation is displayed</t>
+  </si>
+  <si>
+    <t>TC-029</t>
+  </si>
+  <si>
+    <t>Password field masking</t>
+  </si>
+  <si>
+    <t>Enter a password in the password field</t>
+  </si>
+  <si>
+    <t>Password characters are masked</t>
+  </si>
+  <si>
+    <t>UI / Security</t>
+  </si>
+  <si>
+    <t>TC-030</t>
+  </si>
+  <si>
+    <t>Login button behavior</t>
+  </si>
+  <si>
+    <t>Click Sign in once with valid credentials</t>
+  </si>
+  <si>
+    <t>Application processes login without duplicate submissions or unexpected behavior</t>
+  </si>
+  <si>
+    <t>TC-031</t>
+  </si>
+  <si>
+    <t>Dashboard page refresh</t>
+  </si>
+  <si>
+    <t>Open telemetry dashboard and refresh the browser</t>
+  </si>
+  <si>
+    <t>Dashboard reloads successfully and widgets are displayed</t>
+  </si>
+  <si>
+    <t>Reliability</t>
+  </si>
+  <si>
+    <t>TC-032</t>
+  </si>
+  <si>
+    <t>Browser navigation after login</t>
+  </si>
+  <si>
+    <t>Navigate back and forward after opening dashboard</t>
+  </si>
+  <si>
+    <t>Application handles browser navigation correctly</t>
+  </si>
+  <si>
+    <t>UI / Navigation</t>
+  </si>
+  <si>
+    <t>TC-033</t>
+  </si>
+  <si>
+    <t>Dashboard loading state</t>
+  </si>
+  <si>
+    <t>Open Device Telemetry Dashboard</t>
+  </si>
+  <si>
+    <t>Loading indicator is shown appropriately and eventually disappears</t>
+  </si>
+  <si>
+    <t>TC-034</t>
+  </si>
+  <si>
+    <t>Widget rendering after dashboard load</t>
+  </si>
+  <si>
+    <t>Wait for dashboard loading to complete</t>
+  </si>
+  <si>
+    <t>All required widgets render without overlap or broken UI</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>TC-035</t>
+  </si>
+  <si>
+    <t>Widget label accuracy</t>
+  </si>
+  <si>
+    <t>Compare all displayed widget labels against expected names</t>
+  </si>
+  <si>
+    <t>Labels are correct and consistently displayed</t>
+  </si>
+  <si>
+    <t>UI / Data Validation</t>
+  </si>
+  <si>
+    <t>TC-036</t>
+  </si>
+  <si>
+    <t>Special characters in login fields</t>
+  </si>
+  <si>
+    <t>Enter special characters in username/password</t>
+  </si>
+  <si>
+    <t>Application handles input safely and displays appropriate authentication/validation result</t>
   </si>
 </sst>
 </file>
@@ -889,7 +1036,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E024AC8-D687-7F4F-91F2-5B763D13506A}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="32.33203125" bestFit="1" customWidth="1"/>
@@ -1422,6 +1569,226 @@
         <v>126</v>
       </c>
     </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
